--- a/HSI_FSC_result/4. C Way/result_cway_parameters.xlsx
+++ b/HSI_FSC_result/4. C Way/result_cway_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\4. C Way\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1F3CED-A793-45DF-9707-372B56B41862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136AB384-F125-47A1-A233-BF61EED5DCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="2250" windowWidth="21600" windowHeight="12885" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="64">
   <si>
     <t>murphy</t>
   </si>
@@ -226,6 +226,18 @@
   </si>
   <si>
     <t>30way</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Indian Pines</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>University of Pavia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salinas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -233,9 +245,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -297,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -370,6 +383,12 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3891,13 +3910,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.625" style="28" customWidth="1"/>
     <col min="2" max="7" width="9.75" style="16"/>
     <col min="8" max="8" width="14.125" style="16" customWidth="1"/>
-    <col min="9" max="16384" width="9.75" style="16"/>
+    <col min="9" max="14" width="9.75" style="16"/>
+    <col min="15" max="15" width="17.125" style="16" customWidth="1"/>
+    <col min="16" max="16384" width="9.75" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -4508,7 +4529,256 @@
         <v>52.898951660000002</v>
       </c>
     </row>
+    <row r="36" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="29">
+        <v>5</v>
+      </c>
+      <c r="R36" s="29">
+        <v>10</v>
+      </c>
+      <c r="S36" s="29">
+        <v>15</v>
+      </c>
+      <c r="T36" s="29">
+        <v>20</v>
+      </c>
+      <c r="U36" s="29">
+        <v>25</v>
+      </c>
+      <c r="V36" s="29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O37" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="P37" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="15">
+        <v>57.510976679999999</v>
+      </c>
+      <c r="R37" s="15">
+        <v>52.272416819999997</v>
+      </c>
+      <c r="S37" s="15">
+        <v>54.267733440000001</v>
+      </c>
+      <c r="T37" s="15">
+        <v>53.724088379999998</v>
+      </c>
+      <c r="U37" s="15">
+        <v>56.832861739999998</v>
+      </c>
+      <c r="V37" s="15">
+        <v>57.807590980000001</v>
+      </c>
+    </row>
+    <row r="38" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O38" s="30"/>
+      <c r="P38" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="15">
+        <v>56.165791149999997</v>
+      </c>
+      <c r="R38" s="15">
+        <v>51.833132509999999</v>
+      </c>
+      <c r="S38" s="15">
+        <v>52.307707069999999</v>
+      </c>
+      <c r="T38" s="15">
+        <v>52.591433850000001</v>
+      </c>
+      <c r="U38" s="15">
+        <v>55.641638929999999</v>
+      </c>
+      <c r="V38" s="15">
+        <v>56.7189014</v>
+      </c>
+    </row>
+    <row r="39" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O39" s="30"/>
+      <c r="P39" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q39" s="15">
+        <v>52.760614709999999</v>
+      </c>
+      <c r="R39" s="15">
+        <v>47.210971659999998</v>
+      </c>
+      <c r="S39" s="15">
+        <v>49.030185629999998</v>
+      </c>
+      <c r="T39" s="15">
+        <v>48.784211839999998</v>
+      </c>
+      <c r="U39" s="15">
+        <v>52.219662649999997</v>
+      </c>
+      <c r="V39" s="15">
+        <v>52.898951660000002</v>
+      </c>
+    </row>
+    <row r="40" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O40" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="P40" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="21">
+        <v>75.383392560000004</v>
+      </c>
+      <c r="R40" s="21">
+        <v>72.947680939999998</v>
+      </c>
+      <c r="S40" s="21">
+        <v>73.121610250000003</v>
+      </c>
+      <c r="T40" s="21">
+        <v>73.654300629999994</v>
+      </c>
+      <c r="U40" s="21">
+        <v>72.462829619999994</v>
+      </c>
+      <c r="V40" s="21">
+        <v>71.861090329999996</v>
+      </c>
+    </row>
+    <row r="41" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O41" s="30"/>
+      <c r="P41" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="21">
+        <v>75.281987790000002</v>
+      </c>
+      <c r="R41" s="21">
+        <v>72.314783329999997</v>
+      </c>
+      <c r="S41" s="21">
+        <v>71.550779340000005</v>
+      </c>
+      <c r="T41" s="21">
+        <v>71.89961022</v>
+      </c>
+      <c r="U41" s="21">
+        <v>71.099057200000004</v>
+      </c>
+      <c r="V41" s="21">
+        <v>72.762534619999997</v>
+      </c>
+    </row>
+    <row r="42" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O42" s="30"/>
+      <c r="P42" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="21">
+        <v>69.011206389999998</v>
+      </c>
+      <c r="R42" s="21">
+        <v>65.92363349</v>
+      </c>
+      <c r="S42" s="21">
+        <v>66.180280109999998</v>
+      </c>
+      <c r="T42" s="21">
+        <v>66.739814120000005</v>
+      </c>
+      <c r="U42" s="21">
+        <v>65.502145040000002</v>
+      </c>
+      <c r="V42" s="21">
+        <v>64.815161200000006</v>
+      </c>
+    </row>
+    <row r="43" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O43" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="P43" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="15">
+        <v>87.239187869999995</v>
+      </c>
+      <c r="R43" s="15">
+        <v>85.621940179999996</v>
+      </c>
+      <c r="S43" s="15">
+        <v>86.209979860000004</v>
+      </c>
+      <c r="T43" s="15">
+        <v>86.866727460000007</v>
+      </c>
+      <c r="U43" s="15">
+        <v>86.998281879999993</v>
+      </c>
+      <c r="V43" s="15">
+        <v>85.937297939999993</v>
+      </c>
+    </row>
+    <row r="44" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O44" s="30"/>
+      <c r="P44" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q44" s="15">
+        <v>89.952317480000005</v>
+      </c>
+      <c r="R44" s="15">
+        <v>89.289302829999997</v>
+      </c>
+      <c r="S44" s="15">
+        <v>90.294181699999996</v>
+      </c>
+      <c r="T44" s="15">
+        <v>90.425407340000007</v>
+      </c>
+      <c r="U44" s="15">
+        <v>89.206274750000006</v>
+      </c>
+      <c r="V44" s="15">
+        <v>90.394602419999998</v>
+      </c>
+    </row>
+    <row r="45" spans="15:22" x14ac:dyDescent="0.2">
+      <c r="O45" s="30"/>
+      <c r="P45" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="15">
+        <v>85.863798279999997</v>
+      </c>
+      <c r="R45" s="15">
+        <v>84.053196150000005</v>
+      </c>
+      <c r="S45" s="15">
+        <v>84.727869929999997</v>
+      </c>
+      <c r="T45" s="15">
+        <v>85.43888647</v>
+      </c>
+      <c r="U45" s="15">
+        <v>85.583565449999995</v>
+      </c>
+      <c r="V45" s="15">
+        <v>84.423196009999998</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="O37:O39"/>
+    <mergeCell ref="O40:O42"/>
+    <mergeCell ref="O43:O45"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5659,14 +5929,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ECECFB-2829-4B57-BBBC-414CB111007E}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.125" style="1" customWidth="1"/>
     <col min="2" max="16384" width="10.125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -5675,7 +5945,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
@@ -5685,8 +5955,11 @@
       <c r="C2" s="11">
         <v>93.298509170000003</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I2" s="5">
+        <v>86.943479999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>46</v>
       </c>
@@ -5699,8 +5972,11 @@
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I3" s="3">
+        <v>78.315444999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>47</v>
       </c>
@@ -5713,8 +5989,11 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I4" s="3">
+        <v>79.130430000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>48</v>
       </c>
@@ -5727,8 +6006,11 @@
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I5" s="3">
+        <v>75.098190000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>53</v>
       </c>
@@ -5741,8 +6023,11 @@
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I6" s="3">
+        <v>89.744606000000005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>49</v>
       </c>
@@ -5755,8 +6040,11 @@
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I7" s="3">
+        <v>65.301109999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>50</v>
       </c>
@@ -5769,8 +6057,11 @@
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I8" s="3">
+        <v>84.840999999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
@@ -5783,8 +6074,11 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I9" s="3">
+        <v>87.497380000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>52</v>
       </c>
@@ -5797,8 +6091,11 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I10" s="3">
+        <v>67.932929999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>1</v>
       </c>
@@ -5811,8 +6108,11 @@
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I11" s="3">
+        <v>84.161621441119607</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>2</v>
       </c>
@@ -5825,8 +6125,11 @@
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I12" s="3">
+        <v>79.422736167907701</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>3</v>
       </c>
@@ -5839,6 +6142,9 @@
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
+      <c r="I13" s="3">
+        <v>79.685225351475097</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
